--- a/data/trans_dic/P1404-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P1404-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,13%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,0; 8,8</t>
+          <t>4,97; 8,87</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10,69; 15,68</t>
+          <t>10,59; 15,79</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10,25; 15,6</t>
+          <t>10,0; 15,1</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12,53; 17,88</t>
+          <t>12,54; 17,42</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,9; 12,49</t>
+          <t>7,83; 12,31</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,43; 18,3</t>
+          <t>12,41; 18,25</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,46; 18,23</t>
+          <t>12,76; 18,4</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>15,71; 19,73</t>
+          <t>15,37; 19,39</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7,01; 9,89</t>
+          <t>6,92; 9,75</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12,37; 16,14</t>
+          <t>12,13; 16,18</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11,93; 15,7</t>
+          <t>12,02; 15,75</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>14,63; 17,96</t>
+          <t>14,62; 17,77</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>14,76%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,24; 11,07</t>
+          <t>7,37; 11,06</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9,41; 13,37</t>
+          <t>9,4; 13,34</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9,91; 14,0</t>
+          <t>10,05; 14,11</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,94; 14,7</t>
+          <t>11,85; 15,98</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>9,48; 13,64</t>
+          <t>9,54; 13,65</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,95; 16,41</t>
+          <t>11,8; 16,38</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,42; 16,99</t>
+          <t>12,4; 17,27</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>13,92; 17,52</t>
+          <t>14,07; 17,47</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>8,82; 11,64</t>
+          <t>8,88; 11,7</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11,33; 14,3</t>
+          <t>11,31; 14,29</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11,83; 15,04</t>
+          <t>11,88; 15,06</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,8; 15,15</t>
+          <t>13,45; 16,08</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>32,18%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>14,37%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,53; 9,56</t>
+          <t>5,61; 9,52</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,85; 12,77</t>
+          <t>7,81; 12,91</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10,14; 15,09</t>
+          <t>10,12; 14,79</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12,87; 18,35</t>
+          <t>12,97; 17,93</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8,65; 13,31</t>
+          <t>8,71; 13,39</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,43; 15,44</t>
+          <t>10,14; 15,58</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,8; 13,57</t>
+          <t>9,02; 13,86</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>12,38; 65,5</t>
+          <t>11,37; 15,42</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7,73; 10,77</t>
+          <t>7,79; 10,77</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9,84; 13,63</t>
+          <t>9,68; 13,12</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10,3; 13,57</t>
+          <t>10,29; 13,63</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>13,66; 52,5</t>
+          <t>12,77; 16,02</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,85%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,56; 9,95</t>
+          <t>6,66; 9,95</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,97; 13,44</t>
+          <t>9,19; 13,76</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,57; 11,37</t>
+          <t>7,61; 11,5</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12,03; 16,07</t>
+          <t>11,89; 15,85</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,52; 11,01</t>
+          <t>7,31; 11,13</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,4; 15,96</t>
+          <t>11,37; 15,6</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,1; 14,54</t>
+          <t>10,09; 14,33</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>14,01; 19,53</t>
+          <t>15,9; 19,64</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,54; 9,99</t>
+          <t>7,43; 9,95</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10,77; 13,82</t>
+          <t>10,99; 14,04</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9,34; 12,35</t>
+          <t>9,43; 12,42</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>13,89; 17,27</t>
+          <t>14,62; 17,38</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>15,26%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,02; 8,9</t>
+          <t>6,95; 8,88</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>10,2; 12,53</t>
+          <t>10,26; 12,66</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10,41; 12,58</t>
+          <t>10,41; 12,51</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10,6; 14,93</t>
+          <t>13,3; 15,62</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,25; 11,4</t>
+          <t>9,24; 11,34</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,61; 15,0</t>
+          <t>12,56; 14,97</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,1; 14,5</t>
+          <t>12,06; 14,51</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>15,67; 35,12</t>
+          <t>15,14; 17,0</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8,44; 9,89</t>
+          <t>8,45; 9,83</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11,79; 13,39</t>
+          <t>11,77; 13,4</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11,56; 13,19</t>
+          <t>11,48; 13,19</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>14,35; 27,09</t>
+          <t>14,56; 15,99</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>94653</t>
+          <t>102956</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>118801</t>
+          <t>126463</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>213454</t>
+          <t>229419</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>34675; 61043</t>
+          <t>34478; 61587</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>75195; 110301</t>
+          <t>74521; 111084</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>69148; 105302</t>
+          <t>67463; 101912</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>79557; 113500</t>
+          <t>86570; 120247</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>54375; 85988</t>
+          <t>53918; 84767</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>86637; 127587</t>
+          <t>86511; 127230</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>83832; 122660</t>
+          <t>85822; 123807</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>106029; 133175</t>
+          <t>112488; 141946</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>96930; 136712</t>
+          <t>95639; 134785</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>173186; 226040</t>
+          <t>169923; 226582</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>160806; 211512</t>
+          <t>161934; 212220</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>191591; 235167</t>
+          <t>207914; 252678</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>132194</t>
+          <t>145288</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>150594</t>
+          <t>166759</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>282787</t>
+          <t>312047</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>69661; 106463</t>
+          <t>70870; 106357</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>95793; 136128</t>
+          <t>95639; 135774</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>101351; 143163</t>
+          <t>102777; 144257</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>58849; 175020</t>
+          <t>123995; 167254</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>91756; 132071</t>
+          <t>92420; 132209</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>122974; 168813</t>
+          <t>121410; 168520</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>129565; 177231</t>
+          <t>129340; 180086</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>132979; 167354</t>
+          <t>150198; 186550</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>170199; 224647</t>
+          <t>171318; 225877</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>231983; 292758</t>
+          <t>231537; 292483</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>244271; 310549</t>
+          <t>245270; 311004</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>188914; 325095</t>
+          <t>284411; 339908</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>107777</t>
+          <t>122724</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>299899</t>
+          <t>108231</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>407676</t>
+          <t>230955</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>37555; 64885</t>
+          <t>38036; 64565</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>59330; 96565</t>
+          <t>59050; 97625</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>76988; 114616</t>
+          <t>76834; 112368</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>90095; 128481</t>
+          <t>103510; 143101</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>59165; 91013</t>
+          <t>59557; 91591</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>81082; 120011</t>
+          <t>78798; 121053</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>69071; 106560</t>
+          <t>70801; 108804</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>115399; 610314</t>
+          <t>92059; 124868</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>105260; 146761</t>
+          <t>106104; 146741</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>150866; 208958</t>
+          <t>148400; 201145</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>159119; 209647</t>
+          <t>158936; 210563</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>222962; 856711</t>
+          <t>205315; 257588</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>130027</t>
+          <t>135637</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>187025</t>
+          <t>198032</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>317052</t>
+          <t>333669</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>61799; 93731</t>
+          <t>62780; 93775</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>84995; 127349</t>
+          <t>87134; 130391</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>71013; 106571</t>
+          <t>71323; 107834</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>111372; 148859</t>
+          <t>117635; 156808</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>78061; 114368</t>
+          <t>75911; 115563</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>119954; 167834</t>
+          <t>119570; 164087</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>105439; 151817</t>
+          <t>105268; 149557</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>152801; 213090</t>
+          <t>177519; 219249</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>149355; 197823</t>
+          <t>147142; 197131</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>215348; 276389</t>
+          <t>219783; 280807</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>185117; 244724</t>
+          <t>186823; 246002</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>280104; 348317</t>
+          <t>307861; 366083</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>464651</t>
+          <t>506606</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>756318</t>
+          <t>599485</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1220969</t>
+          <t>1106090</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>229997; 291763</t>
+          <t>227814; 290827</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>349516; 429276</t>
+          <t>351376; 433553</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>353501; 427026</t>
+          <t>353223; 424568</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>365988; 515380</t>
+          <t>468873; 550434</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>312640; 385338</t>
+          <t>312230; 383320</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>448403; 533428</t>
+          <t>446382; 532027</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>428803; 514035</t>
+          <t>427646; 514429</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>572572; 1282956</t>
+          <t>564001; 633319</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>561635; 658087</t>
+          <t>562402; 654366</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>822841; 934543</t>
+          <t>821373; 935342</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>802335; 915480</t>
+          <t>796559; 914997</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1019748; 1924356</t>
+          <t>1055483; 1159513</t>
         </is>
       </c>
     </row>
